--- a/results/02_taxa_assemblage/AU-Sweeping/tables/k3_popout_atypical_sites.xlsx
+++ b/results/02_taxa_assemblage/AU-Sweeping/tables/k3_popout_atypical_sites.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DR-94</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4749</v>
+        <v>0.4623</v>
       </c>
       <c r="F2" t="n">
-        <v>0.056</v>
+        <v>0.008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4189</v>
+        <v>0.4543</v>
       </c>
     </row>
     <row r="3">
@@ -491,23 +491,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4749</v>
+        <v>0.6341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.064</v>
+        <v>0.038</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4109</v>
+        <v>0.5961</v>
       </c>
     </row>
     <row r="4">
@@ -516,98 +516,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.4573</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1663</v>
+        <v>0.038</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4763</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DR-143</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>46</v>
-      </c>
-      <c r="D5" t="n">
-        <v>42</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6643</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0138</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6505</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LSC-07</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>52</v>
-      </c>
-      <c r="D6" t="n">
-        <v>47</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8545</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.4566</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3979</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DR-85</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>74</v>
-      </c>
-      <c r="D7" t="n">
-        <v>68</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.7156</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6916</v>
+        <v>0.4193</v>
       </c>
     </row>
   </sheetData>
